--- a/JasonPlayground/gcp_medallion_learning_path_instruction_guide.xlsx
+++ b/JasonPlayground/gcp_medallion_learning_path_instruction_guide.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start_Here" sheetId="1" r:id="Re880ece1ce4d495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Project_Management" sheetId="2" r:id="R6fab380aa7604f65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_VSCode_Git_GitHub" sheetId="3" r:id="Rd1bffeba1a5b426a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GCP_Setup" sheetId="4" r:id="R7d4dfdd93d5843d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Datasets_Bronze_GCS" sheetId="5" r:id="Ra9191574009f49f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dataproc_Spark" sheetId="6" r:id="Rec581eea96d64096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_BigQuery_Gold" sheetId="7" r:id="R4fef2a59f4f848b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Composer_Airflow" sheetId="8" r:id="R7ce49e93989f4767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Cleanup" sheetId="9" r:id="R4f3f1d025efc48a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D01_Project_Management" sheetId="10" r:id="R2d2e7fe2a7434ae9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D02_VSCode_Terminal" sheetId="11" r:id="R0df602e6441f49ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D03_Git_GitHub" sheetId="12" r:id="R13d9fc8dc92846df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D04_GCP_Account_CLI" sheetId="13" r:id="Rffd424e5475844c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D05_GCS_Bronze" sheetId="14" r:id="R5108361f417b41f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D06_Dataproc_SSH" sheetId="15" r:id="R3c20ecd625d34d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D07_Spark_Silver" sheetId="16" r:id="Rfee7be079b0f4fb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D08_BigQuery_Gold" sheetId="17" r:id="R07075b636f7b4106"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D09_Composer_Airflow" sheetId="18" r:id="R70acc3e5f61246e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D10_Cleanup" sheetId="19" r:id="R318d97ecc2d642c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start_Here" sheetId="1" r:id="R2776f9142c4148a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Project_Management" sheetId="2" r:id="Rfb32d7e973f243e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_VSCode_Git_GitHub" sheetId="3" r:id="R4a76a11f695646a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_GCP_Setup" sheetId="4" r:id="R9efc152139c141f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Datasets_Bronze_GCS" sheetId="5" r:id="Reda14133bde04104"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Dataproc_Spark" sheetId="6" r:id="Ra27f273a3d594fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_BigQuery_Gold" sheetId="7" r:id="Ra7f7e0f0a4e146da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_Composer_Airflow" sheetId="8" r:id="Rd12b45f1d82647d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Cleanup" sheetId="9" r:id="R27b89eafcce54196"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D01_Project_Management" sheetId="10" r:id="R51930ca3b1494700"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D02_VSCode_Terminal" sheetId="11" r:id="R2334c9c6df6a41f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D03_Git_GitHub" sheetId="12" r:id="R8b1e627765c84759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D04_GCP_Account_CLI" sheetId="13" r:id="R2659f547e9a94731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D05_GCS_Bronze" sheetId="14" r:id="Rd05d24b52d6f45ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D06_Dataproc_SSH" sheetId="15" r:id="R733f5c2b7cfb4aab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D07_Spark_Silver" sheetId="16" r:id="R636095e466824669"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D08_BigQuery_Gold" sheetId="17" r:id="Rde018e11726e43c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D09_Composer_Airflow" sheetId="18" r:id="R758f7c1fd10942da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D10_Cleanup" sheetId="19" r:id="R0d0953a2da184715"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -87,7 +87,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Codex" id="{2B2B9D46-A93D-4B23-8BC8-74C5DBEC9364}"/>
+  <xltc:person displayName="Codex" id="{006722CB-4C1F-47B6-83FE-FA050D2FC07F}"/>
 </xltc:personList>
 </file>
 
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Tbl_D04GCPAccountCLI" displayName="Tbl_D04GCPAccountCLI" ref="A1:G15" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Tbl_D04GCPAccountCLI" displayName="Tbl_D04GCPAccountCLI" ref="A1:G26" headerRowCount="1">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="Step"/>
     <x:tableColumn id="2" name="Where you are"/>
@@ -731,7 +731,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra75855e0f40a4799"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3109e80cecc14640"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1255,7 +1255,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raee84466467b4007"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60f00d5454c543dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1651,7 +1651,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2d21e3a698b4b83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6402c5a64c6c44ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2089,7 +2089,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669ca94830af40c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a202ac33aae42d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2138,19 +2138,19 @@
         <x:v>Browser</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>You need a GCP account and billing awareness.</x:v>
+        <x:v>You only have a Google account, not Google Cloud setup yet.</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Open Google Cloud Console.</x:v>
+        <x:v>Open the Google Cloud free/start page.</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>https://console.cloud.google.com/</x:v>
+        <x:v>https://cloud.google.com/free</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>If asked to accept terms, read and accept if you are comfortable.</x:v>
+        <x:v>If the page wording changes, look for Start free, Get started for free, or Console.</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>Console opens.</x:v>
+        <x:v>You see a Google Cloud signup/start option.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2158,23 +2158,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>Console</x:v>
+        <x:v>Google Cloud start page</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>You may see project selector at top.</x:v>
+        <x:v>You may be asked to sign in.</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Create or select a dedicated learning project.</x:v>
+        <x:v>Sign in using the Google account you want to use for this learning project.</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>Top project selector &gt; New Project
-Name: Jason GCP DE Playground</x:v>
+        <x:v>Click Sign in or Get started for free, then choose your Google account.</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
-        <x:v>If organization restrictions block creation, use an existing personal project.</x:v>
+        <x:v>If you are signed into several Google accounts, choose the one you are comfortable linking to Cloud Billing.</x:v>
       </x:c>
       <x:c r="G3" s="6" t="str">
-        <x:v>You have a project.</x:v>
+        <x:v>You are signed in and see Google Cloud setup screens.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2182,22 +2181,24 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>Console</x:v>
+        <x:v>Google Cloud setup</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>Project ID is globally unique and may differ from name.</x:v>
+        <x:v>Google may ask for country, account type, name/address, and payment method.</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>Copy the Project ID to your private notes.</x:v>
+        <x:v>Complete the first-time Google Cloud setup. This creates or prepares a self-serve Cloud Billing account for Google Cloud usage.</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>Example: jason-gcp-de-playground-123</x:v>
+        <x:v>Follow the on-screen setup form.
+Use your real country/billing details.
+Read any free trial/credit information shown.</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Do not use this exact example unless it is your actual project id.</x:v>
+        <x:v>If you do not want to add a payment method, stop here. Dataproc/Composer require billing-enabled Google Cloud.</x:v>
       </x:c>
       <x:c r="G4" s="6" t="str">
-        <x:v>PROJECT_ID is known.</x:v>
+        <x:v>You can enter Google Cloud Console.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2205,22 +2206,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>Console Billing</x:v>
+        <x:v>Google Cloud setup</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>Billing must be understood before resources.</x:v>
+        <x:v>Google may mention free trial credits, automatic upgrade, or billing terms.</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>Check Billing page and free trial/credits.</x:v>
+        <x:v>Read the billing/free trial screen carefully before accepting.</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>Console menu &gt; Billing</x:v>
+        <x:v>Manual review only.</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
-        <x:v>If you cannot access billing, stop before creating Dataproc or Composer.</x:v>
+        <x:v>If the terms differ from what you expected, pause and ask Codex before continuing.</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
-        <x:v>You know billing status.</x:v>
+        <x:v>You understand whether you are on free trial and what happens after credits/trial.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2228,181 +2229,436 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>Console Billing</x:v>
+        <x:v>Cloud Console</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
+        <x:v>After signup you may land on a welcome page, dashboard, or project picker.</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>Open Cloud Console if not already there.</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>https://console.cloud.google.com/</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>If you land on a Google Cloud marketing page, click Console.</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>Google Cloud Console opens.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="6" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Cloud Console</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>You need a dedicated learning project.</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>Open the project selector.</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>Click the project dropdown near the top of the Console.</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>If no project exists yet, Google may show Create project directly.</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>You see project picker or Manage resources.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="6" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Project picker</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>You need to create a new project.</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>Click New Project.</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>Project picker &gt; New Project</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>If New Project is missing, go to: https://console.cloud.google.com/cloud-resource-manager</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>New Project form opens.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="6" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>New Project form</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>Project name is human-readable and can be changed later.</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>Enter project name.</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>Project name: Jason GCP DE Playground</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>If you prefer another name, use it. Do not put sensitive info in project names.</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>Project name is filled.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="6" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>New Project form</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>Project ID is permanent and globally unique.</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>Review or edit the Project ID before creating.</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>Suggested pattern: jason-gcp-de-playground-&lt;shortnumber&gt;
+Rules: lowercase letters, numbers, hyphens, 6-30 chars, starts with a letter, cannot end with hyphen.</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>If Google generated an ID, using it is fine. Copy it exactly.</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>PROJECT_ID is decided and saved in your notes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="6" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>New Project form</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>Billing account may be selected automatically after signup.</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>Make sure the project is linked to the billing account created during setup.</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>Billing account field: select your self-serve/free trial billing account if shown.</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>If no billing account is available, go back to Billing setup. You cannot use Dataproc/Composer without billing.</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>Project is ready to create.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="6" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>New Project form</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>Location/organization may show No organization for personal accounts.</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>Leave location as No organization if that is what you see.</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>Location: No organization</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>If you see an organization because this is a work/school account, consider using a personal Google account instead for learning.</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>Location is acceptable.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="6" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>New Project form</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>Create button should now be available.</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>Create the project.</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>Click Create.</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>Project creation can take a minute.</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>Project exists.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="6" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Cloud Console</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>Console may still be on another project.</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>Switch to your new project.</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>Top project dropdown &gt; select Jason GCP DE Playground / your PROJECT_ID.</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>If you cannot find it, refresh or open Manage resources.</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>Active project is your learning project.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="6" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Cloud Console</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>You need to copy identifiers.</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>Find and save project ID and project number.</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>Console Home/Dashboard or Project info card.
+Copy: Project name, Project ID, Project number.</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>Project ID is the value used in commands, not project name.</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>PROJECT_ID is saved in a private note.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="6" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>Cloud Billing</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>Before resources, verify billing is linked.</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="str">
+        <x:v>Open Billing for the selected project.</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="str">
+        <x:v>Console menu &gt; Billing</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="str">
+        <x:v>If it asks to link billing, link the billing account created in setup.</x:v>
+      </x:c>
+      <x:c r="G16" s="6" t="str">
+        <x:v>Billing is linked to the project.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="6" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>Cloud Billing</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
         <x:v>Budget alert protects you.</x:v>
       </x:c>
-      <x:c r="D6" s="6" t="str">
-        <x:v>Create budget alert.</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="str">
+      <x:c r="D17" s="6" t="str">
+        <x:v>Create budget alert before any Dataproc or Composer work.</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="str">
         <x:v>Billing &gt; Budgets and alerts &gt; Create budget
 Scope: your PROJECT_ID
 Amount: 5 or 10 USD
 Alerts: 50%, 80%, 100%</x:v>
       </x:c>
-      <x:c r="F6" s="6" t="str">
+      <x:c r="F17" s="6" t="str">
         <x:v>Choose an amount you are comfortable with.</x:v>
       </x:c>
-      <x:c r="G6" s="6" t="str">
+      <x:c r="G17" s="6" t="str">
         <x:v>Budget alert exists.</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="6" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="str">
+    <x:row r="18">
+      <x:c r="A18" s="6" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
         <x:v>VS Code terminal</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C18" s="6" t="str">
         <x:v>Google Cloud CLI may not be installed.</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D18" s="6" t="str">
         <x:v>Check gcloud.</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
+      <x:c r="E18" s="6" t="str">
         <x:v>gcloud --version</x:v>
       </x:c>
-      <x:c r="F7" s="6" t="str">
-        <x:v>If command not found, install Google Cloud CLI and restart VS Code.</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="str">
+      <x:c r="F18" s="6" t="str">
+        <x:v>If command not found, install Google Cloud CLI from https://cloud.google.com/sdk/docs/install and restart VS Code.</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="str">
         <x:v>gcloud version prints.</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="6" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="str">
+    <x:row r="19">
+      <x:c r="A19" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
         <x:v>Authenticate CLI.</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
-        <x:v>Login with your Google account.</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="str">
+      <x:c r="D19" s="6" t="str">
+        <x:v>Login with the same Google account used for Cloud setup.</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="str">
         <x:v>gcloud auth login</x:v>
       </x:c>
-      <x:c r="F8" s="6" t="str">
+      <x:c r="F19" s="6" t="str">
         <x:v>Use the same account as your GCP project.</x:v>
       </x:c>
-      <x:c r="G8" s="6" t="str">
+      <x:c r="G19" s="6" t="str">
         <x:v>Browser login completes.</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="6" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
+    <x:row r="20">
+      <x:c r="A20" s="6" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
         <x:v>Set active project.</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>Replace PROJECT_ID.</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="str">
+      <x:c r="D20" s="6" t="str">
+        <x:v>Replace PROJECT_ID with the permanent Project ID you copied.</x:v>
+      </x:c>
+      <x:c r="E20" s="6" t="str">
         <x:v>gcloud config set project PROJECT_ID</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="str">
-        <x:v>Use copied project id, not project display name.</x:v>
-      </x:c>
-      <x:c r="G9" s="6" t="str">
+      <x:c r="F20" s="6" t="str">
+        <x:v>Use project id, not project display name.</x:v>
+      </x:c>
+      <x:c r="G20" s="6" t="str">
         <x:v>Active project is set.</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="6" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="str">
+    <x:row r="21">
+      <x:c r="A21" s="6" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B21" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C21" s="6" t="str">
         <x:v>Verify active project.</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D21" s="6" t="str">
         <x:v>List config.</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
+      <x:c r="E21" s="6" t="str">
         <x:v>gcloud config list</x:v>
       </x:c>
-      <x:c r="F10" s="6" t="str">
+      <x:c r="F21" s="6" t="str">
         <x:v>If project is wrong, set it again.</x:v>
       </x:c>
-      <x:c r="G10" s="6" t="str">
+      <x:c r="G21" s="6" t="str">
         <x:v>Correct project appears.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="6" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
+    <x:row r="22">
+      <x:c r="A22" s="6" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
         <x:v>Choose region/zone.</x:v>
       </x:c>
-      <x:c r="D11" s="6" t="str">
+      <x:c r="D22" s="6" t="str">
         <x:v>Use one region consistently. us-central1 is common for learning; asia-southeast1 may be closer to Manila but can vary in availability/cost.</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="str">
+      <x:c r="E22" s="6" t="str">
         <x:v>gcloud config set compute/region REGION
 gcloud config set compute/zone ZONE</x:v>
       </x:c>
-      <x:c r="F11" s="6" t="str">
+      <x:c r="F22" s="6" t="str">
         <x:v>REGION, ZONE</x:v>
       </x:c>
-      <x:c r="G11" s="6" t="str">
+      <x:c r="G22" s="6" t="str">
         <x:v>Region/zone defaults are set.</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="6" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="str">
+    <x:row r="23">
+      <x:c r="A23" s="6" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
         <x:v>Verify region/zone.</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D23" s="6" t="str">
         <x:v>Read defaults.</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
+      <x:c r="E23" s="6" t="str">
         <x:v>gcloud config get-value compute/region
 gcloud config get-value compute/zone</x:v>
       </x:c>
-      <x:c r="F12" s="6" t="str">
+      <x:c r="F23" s="6" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="G12" s="6" t="str">
+      <x:c r="G23" s="6" t="str">
         <x:v>Correct values print.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="6" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B13" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="str">
+    <x:row r="24">
+      <x:c r="A24" s="6" t="n">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
         <x:v>Enable APIs one by one so errors are clear.</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
+      <x:c r="D24" s="6" t="str">
         <x:v>Run service enable commands.</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
+      <x:c r="E24" s="6" t="str">
         <x:v>gcloud services enable compute.googleapis.com
 gcloud services enable dataproc.googleapis.com
 gcloud services enable storage.googleapis.com
@@ -2412,63 +2668,63 @@
 gcloud services enable secretmanager.googleapis.com
 gcloud services enable logging.googleapis.com</x:v>
       </x:c>
-      <x:c r="F13" s="6" t="str">
+      <x:c r="F24" s="6" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="G13" s="6" t="str">
+      <x:c r="G24" s="6" t="str">
         <x:v>Services enabled.</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="6" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B14" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C14" s="6" t="str">
+    <x:row r="25">
+      <x:c r="A25" s="6" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
         <x:v>Confirm enabled APIs.</x:v>
       </x:c>
-      <x:c r="D14" s="6" t="str">
+      <x:c r="D25" s="6" t="str">
         <x:v>List enabled relevant services.</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="str">
+      <x:c r="E25" s="6" t="str">
         <x:v>gcloud services list --enabled --filter="name:(compute OR dataproc OR storage OR bigquery OR composer)"</x:v>
       </x:c>
-      <x:c r="F14" s="6" t="str">
+      <x:c r="F25" s="6" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="G14" s="6" t="str">
+      <x:c r="G25" s="6" t="str">
         <x:v>Relevant APIs appear.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="6" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B15" s="6" t="str">
-        <x:v>Terminal</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="str">
+    <x:row r="26">
+      <x:c r="A26" s="6" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Terminal</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
         <x:v>Create parameter note.</x:v>
       </x:c>
-      <x:c r="D15" s="6" t="str">
+      <x:c r="D26" s="6" t="str">
         <x:v>Create a local parameters template that should not contain secrets.</x:v>
       </x:c>
-      <x:c r="E15" s="6" t="str">
-        <x:v>Set-Content docs\local_parameters_template.md "# Local Parameters`n`nPROJECT_ID=`nREGION=`nZONE=`nBUCKET=`nCLUSTER=jason-dp-dev`nCOMPOSER_ENV=jason-composer-dev`n"</x:v>
-      </x:c>
-      <x:c r="F15" s="6" t="str">
+      <x:c r="E26" s="6" t="str">
+        <x:v>Set-Content docs\local_parameters_template.md "# Local Parameters`n`nPROJECT_ID=`nPROJECT_NUMBER=`nREGION=`nZONE=`nBUCKET=`nCLUSTER=jason-dp-dev`nCOMPOSER_ENV=jason-composer-dev`n"</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="G15" s="6" t="str">
+      <x:c r="G26" s="6" t="str">
         <x:v>Template exists for your notes. | docs folder does not exist.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5444ea5f1dfb48c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9798ba755a147e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2769,7 +3025,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d5f19c46b024fd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R758ba0be95e94cc3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3140,7 +3396,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6752ec4c9444c5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d0c2ef9dbc0407f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3447,7 +3703,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R574737d9b88145fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05767f015a854f64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3722,7 +3978,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R527eedd1d79b44c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62d0eea2622d4686"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4094,7 +4350,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5390b0abe41e4889"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R410f832cb71d41bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4437,7 +4693,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16d208a5adc040c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf6b65f9d1c645b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4901,7 +5157,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c738ca4dd084570"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d12d44687a45f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5126,7 +5382,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a5cc1e08ab140f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d735fd908ee480c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5302,7 +5558,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8bda55bedfa44ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c2047c1f6474a0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5467,7 +5723,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R316396f9eece4e98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6feedfa38c24a98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5683,7 +5939,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R092c0ef2c9964db7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8db83beb9c0401e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5822,7 +6078,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10e1093d05554053"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R174fc056172b46be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5961,7 +6217,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ae094a3b31749be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R909cba4921814aaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6103,7 +6359,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54d9725bc2754af4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf16bc6b4c874a68"/>
   </x:tableParts>
 </x:worksheet>
 </file>